--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="116">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Personne et/ou Structure (Auteur)</t>
+    <t>Modèle métier - Personne et/ou Structure (Auteur)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,91 +253,11 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">BackboneElement
+    <t xml:space="preserve">Base
 </t>
   </si>
   <si>
     <t>Personne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.personne.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.personne.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.personne.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
     <t>PersonneStructureAuteur.personne.identifiantPersonne</t>
@@ -391,15 +311,6 @@
     <t>Identité de la personne</t>
   </si>
   <si>
-    <t>PersonneStructureAuteur.personne.IdentitePersonne.id</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.personne.IdentitePersonne.extension</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.personne.IdentitePersonne.modifierExtension</t>
-  </si>
-  <si>
     <t>PersonneStructureAuteur.personne.IdentitePersonne.nomPersonne</t>
   </si>
   <si>
@@ -409,6 +320,10 @@
     <t>PersonneStructureAuteur.personne.IdentitePersonne.prenomPersonne</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Prénom de la personne</t>
   </si>
   <si>
@@ -428,15 +343,6 @@
   </si>
   <si>
     <t>Structure</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.structure.id</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.structure.extension</t>
-  </si>
-  <si>
-    <t>PersonneStructureAuteur.structure.modifierExtension</t>
   </si>
   <si>
     <t>PersonneStructureAuteur.structure.identifiantStructure</t>
@@ -770,43 +676,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="66.83203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="66.83203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.44921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.44921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.66015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="65.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="56.44921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -1117,15 +1023,15 @@
         <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1133,10 +1039,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1148,13 +1054,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1205,13 +1111,13 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1222,21 +1128,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1248,17 +1154,15 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>72</v>
@@ -1295,43 +1199,43 @@
         <v>72</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1344,26 +1248,22 @@
         <v>72</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>72</v>
       </c>
@@ -1411,7 +1311,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1423,15 +1323,15 @@
         <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1439,7 +1339,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>74</v>
@@ -1454,13 +1354,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1511,10 +1411,10 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>74</v>
@@ -1528,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1539,7 +1439,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>78</v>
@@ -1554,13 +1454,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1611,10 +1511,10 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>78</v>
@@ -1628,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1639,7 +1539,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>74</v>
@@ -1654,13 +1554,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1711,10 +1611,10 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>74</v>
@@ -1728,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1754,13 +1654,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1811,7 +1711,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1828,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1854,13 +1754,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1911,7 +1811,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1923,15 +1823,15 @@
         <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1954,13 +1854,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2011,7 +1911,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -2028,21 +1928,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2054,17 +1954,15 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>72</v>
@@ -2101,75 +1999,71 @@
         <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>72</v>
       </c>
@@ -2217,27 +2111,27 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2245,11 +2139,11 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
       </c>
@@ -2260,13 +2154,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2317,13 +2211,13 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AG15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
@@ -2334,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2360,13 +2254,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2417,7 +2311,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2434,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2448,7 +2342,7 @@
         <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>72</v>
@@ -2460,13 +2354,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2517,13 +2411,13 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>72</v>
@@ -2534,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2560,13 +2454,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2617,7 +2511,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2629,912 +2523,6 @@
         <v>72</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q22" s="2"/>
-      <c r="R22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q27" s="2"/>
-      <c r="R27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/main/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
